--- a/APACdata.xlsx
+++ b/APACdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokam\PycharmProjects\BarrettAutomate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62A4EA4-CCAD-4375-85F1-DF53CA334255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408CC181-C1F7-42A3-8A33-517FC873FFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="0" windowWidth="17196" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="945" windowWidth="27720" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="36" r:id="rId1"/>
@@ -37,14 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Optic</t>
   </si>
   <si>
-    <t>Biconvex</t>
-  </si>
-  <si>
     <t>PatientName</t>
   </si>
   <si>
@@ -79,12 +76,6 @@
   </si>
   <si>
     <t>Refraction</t>
-  </si>
-  <si>
-    <t>attack01</t>
-  </si>
-  <si>
-    <t>KALADA</t>
   </si>
 </sst>
 </file>
@@ -510,7 +501,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
     <col min="2" max="4" width="13" style="2" customWidth="1"/>
@@ -522,120 +513,88 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>4</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1">
-        <v>105737</v>
-      </c>
-      <c r="D2" s="11">
-        <v>1.88</v>
-      </c>
-      <c r="E2" s="9">
-        <v>118.99</v>
-      </c>
-      <c r="F2" s="7">
-        <v>23.33</v>
-      </c>
-      <c r="G2" s="7">
-        <v>44.75</v>
-      </c>
-      <c r="H2" s="7">
-        <v>44.25</v>
-      </c>
-      <c r="I2" s="7">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="J2" s="7">
-        <v>-0.03</v>
-      </c>
-      <c r="K2" s="9">
-        <v>21.5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="11"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="11"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="1"/>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1"/>
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1"/>
       <c r="D6" s="11"/>
     </row>
-    <row r="7" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1"/>
       <c r="D7" s="11"/>
     </row>
-    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1"/>
       <c r="D8" s="11"/>
     </row>
-    <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1"/>
       <c r="D9" s="11"/>
     </row>
-    <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1"/>
       <c r="D10" s="11"/>
     </row>
-    <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1"/>
       <c r="D11" s="11"/>
     </row>
